--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -594,7 +594,7 @@
     <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
+    <t xml:space="preserve">pattern:$this}
 </t>
   </si>
   <si>

--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-diagnosticreport-microbiology.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -272,7 +272,7 @@
     <t>患者、患者のグループ、デバイス、場所、これらから派生した検体に対して実行された診断的検査の結果と解釈。レポートには、依頼情報や依頼者情報などの臨床コンテキスト（文脈）、および１項目単位の結果、画像、テキストとコード化された解釈、および診断レポートのフォーマットされた表現のいくつかの組み合わせが含まれる。</t>
   </si>
   <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
+    <t>これは単一のレポートを格納することを目的としており、複数のレポートを含む要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。  
 【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
   </si>
   <si>
@@ -491,7 +491,7 @@
     <t>実行者/実施者または他のシステムによってこのレポートに割り当てられた識別子</t>
   </si>
   <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>通常、診断サービスを実施した施設の情報システム（実施者ID、HL7 v2 の filler ID）によって割り当てられる。</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
@@ -840,9 +840,6 @@
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.system</t>
-  </si>
-  <si>
-    <t>http://loinc.org</t>
   </si>
   <si>
     <t>DiagnosticReport.category:first.coding.version</t>
@@ -5209,7 +5206,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>266</v>
+        <v>81</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>81</v>
@@ -5280,7 +5277,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>219</v>
@@ -5394,7 +5391,7 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>226</v>
@@ -5437,10 +5434,10 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>269</v>
+        <v>81</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>81</v>
@@ -5508,7 +5505,7 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>232</v>
@@ -5622,7 +5619,7 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>238</v>
@@ -5738,7 +5735,7 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B37" t="s" s="2">
         <v>247</v>
@@ -5854,14 +5851,14 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5883,10 +5880,10 @@
         <v>179</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5898,7 +5895,7 @@
         <v>81</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>81</v>
@@ -5917,7 +5914,7 @@
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>81</v>
@@ -5935,7 +5932,7 @@
         <v>81</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -5950,28 +5947,28 @@
         <v>103</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -5990,19 +5987,19 @@
         <v>92</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>81</v>
@@ -6051,7 +6048,7 @@
         <v>81</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6066,28 +6063,28 @@
         <v>103</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>289</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>290</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>291</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6106,19 +6103,19 @@
         <v>92</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L40" t="s" s="2">
+      <c r="M40" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M40" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="N40" t="s" s="2">
+      <c r="O40" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>81</v>
@@ -6167,7 +6164,7 @@
         <v>81</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6182,28 +6179,28 @@
         <v>103</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>301</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6222,19 +6219,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L41" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N41" t="s" s="2">
+      <c r="O41" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>81</v>
@@ -6283,7 +6280,7 @@
         <v>81</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6298,28 +6295,28 @@
         <v>103</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL41" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>310</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>311</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6338,19 +6335,19 @@
         <v>92</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>81</v>
@@ -6399,7 +6396,7 @@
         <v>81</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
@@ -6417,25 +6414,25 @@
         <v>81</v>
       </c>
       <c r="AL42" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="AM42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6454,19 +6451,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="L43" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="L43" t="s" s="2">
+      <c r="M43" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="M43" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>327</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>81</v>
@@ -6515,7 +6512,7 @@
         <v>81</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6530,28 +6527,28 @@
         <v>103</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AL43" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6570,19 +6567,19 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M44" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>335</v>
-      </c>
       <c r="O44" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>81</v>
@@ -6631,7 +6628,7 @@
         <v>81</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -6646,24 +6643,24 @@
         <v>103</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AN44" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>331</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6686,19 +6683,19 @@
         <v>81</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="M45" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>81</v>
@@ -6747,7 +6744,7 @@
         <v>81</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
@@ -6765,10 +6762,10 @@
         <v>81</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>81</v>
@@ -6776,14 +6773,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6802,19 +6799,19 @@
         <v>81</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M46" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>348</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>81</v>
@@ -6863,7 +6860,7 @@
         <v>81</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6881,10 +6878,10 @@
         <v>81</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>81</v>
@@ -6892,10 +6889,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6918,16 +6915,16 @@
         <v>81</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L47" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="M47" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6977,7 +6974,7 @@
         <v>81</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -6998,7 +6995,7 @@
         <v>81</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>81</v>
@@ -7006,14 +7003,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7032,19 +7029,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>358</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N48" t="s" s="2">
         <v>359</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N48" t="s" s="2">
+      <c r="O48" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>81</v>
@@ -7093,7 +7090,7 @@
         <v>81</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7111,10 +7108,10 @@
         <v>81</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>81</v>
@@ -7122,10 +7119,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7234,10 +7231,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7348,14 +7345,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7377,10 +7374,10 @@
         <v>137</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>140</v>
@@ -7435,7 +7432,7 @@
         <v>81</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -7464,10 +7461,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7493,16 +7490,16 @@
         <v>191</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="M52" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>81</v>
@@ -7551,7 +7548,7 @@
         <v>81</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>79</v>
@@ -7572,7 +7569,7 @@
         <v>81</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>81</v>
@@ -7580,10 +7577,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7606,13 +7603,13 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>377</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>378</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>379</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7663,7 +7660,7 @@
         <v>81</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>91</v>
@@ -7684,7 +7681,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7692,14 +7689,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7721,14 +7718,14 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7777,7 +7774,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7795,10 +7792,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7806,10 +7803,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7835,13 +7832,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>389</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7870,11 +7867,11 @@
         <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="Z55" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="Z55" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AA55" t="s" s="2">
         <v>81</v>
       </c>
@@ -7891,7 +7888,7 @@
         <v>81</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7909,10 +7906,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7920,10 +7917,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7946,19 +7943,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N56" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N56" t="s" s="2">
+      <c r="O56" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -8007,7 +8004,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8025,10 +8022,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>
